--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,17 +452,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INPUT_TEXT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>txtTimKiem</t>
-        </is>
-      </c>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>${keyword}</t>
+          <t>https://gaubongonline.vn/</t>
         </is>
       </c>
     </row>
@@ -472,15 +468,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>//input[@placeholder="Nhập sản phẩm cần tìm"]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>${field}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>CLICK</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>btnTimKiem</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>//button[@type="submit"]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_NOT_PRESENT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>//div[@class="woocommerce-info"]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -493,13 +537,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,15 +574,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INPUT_TEXT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>txtTimKiem</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -546,15 +590,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CLEAR_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>//input[@placeholder="Nhập sản phẩm cần tìm"]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>CLICK</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>btnTimKiem</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>//button[@type="submit"]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_NOT_PRESENT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>//div[@class="woocommerce-info"]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -567,13 +655,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,17 +692,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INPUT_TEXT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>txtTimKiem</t>
-        </is>
-      </c>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>${keyword}</t>
+          <t>https://gaubongonline.vn/</t>
         </is>
       </c>
     </row>
@@ -624,15 +708,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>//input[@placeholder="Nhập sản phẩm cần tìm"]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>${field}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>CLICK</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>btnTimKiem</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>//button[@type="submit"]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_PRESENT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>//div[@class="woocommerce-info"]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -419,8 +419,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -473,12 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//input[@placeholder="Nhập sản phẩm cần tìm"]</t>
+          <t>txtTimKiem</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>${field}</t>
+          <t>${keyword}</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//button[@type="submit"]</t>
+          <t>btnTimKiem</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -504,12 +504,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERIFY_ELEMENT_NOT_PRESENT</t>
+          <t>VERIFY_ELEMENT_PRESENT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//div[@class="woocommerce-info"]</t>
+          <t>txtTimThay</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -541,8 +541,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -595,7 +595,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//input[@placeholder="Nhập sản phẩm cần tìm"]</t>
+          <t>txtTimKiem</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//button[@type="submit"]</t>
+          <t>btnTimKiem</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -622,12 +622,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERIFY_ELEMENT_NOT_PRESENT</t>
+          <t>VERIFY_ELEMENT_PRESENT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//div[@class="woocommerce-info"]</t>
+          <t>txtTimThay</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -659,9 +659,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="61" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -713,12 +713,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//input[@placeholder="Nhập sản phẩm cần tìm"]</t>
+          <t>txtTimKiem</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>${field}</t>
+          <t>${keyword}</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//button[@type="submit"]</t>
+          <t>btnTimKiem</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -744,15 +744,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERIFY_ELEMENT_PRESENT</t>
+          <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//div[@class="woocommerce-info"]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>txtKoTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -415,11 +415,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>${keyword}</t>
+          <t>gấu bông tròn</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERIFY_ELEMENT_PRESENT</t>
+          <t>WAIT_FOR_ELEMENT_VISIBLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -520,11 +520,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>VERIFY_ELEMENT_PRESENT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>txtTimThay</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>CLOSE_BROWSER</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -537,11 +553,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
@@ -622,7 +638,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERIFY_ELEMENT_PRESENT</t>
+          <t>WAIT_FOR_ELEMENT_VISIBLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -638,11 +654,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>VERIFY_ELEMENT_PRESENT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>txtTimThay</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>CLOSE_BROWSER</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -655,13 +687,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="61" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -718,7 +750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>${keyword}</t>
+          <t>bông máy bay</t>
         </is>
       </c>
     </row>
@@ -744,7 +776,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
+          <t>WAIT_FOR_ELEMENT_VISIBLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -752,11 +784,7 @@
           <t>txtKoTimThay</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -764,11 +792,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>VERIFY_TEXT_CONTAINS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>txtKoTimThay</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>CLOSE_BROWSER</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -1,105 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ án 4\DoAn4\scripts\DoAn4_Bemori\AI\TestCase\scripts\SCR\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4624F645-8A35-4C73-BC2D-F2ACC8330B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TC_001" sheetId="1" r:id="rId1"/>
-    <sheet name="TC_002" sheetId="2" r:id="rId2"/>
-    <sheet name="TC_003" sheetId="3" r:id="rId3"/>
+    <sheet name="TC_001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TC_002" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC_003" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="20">
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>KEYWORD</t>
-  </si>
-  <si>
-    <t>LOCATOR</t>
-  </si>
-  <si>
-    <t>VALUE</t>
-  </si>
-  <si>
-    <t>OPEN_URL</t>
-  </si>
-  <si>
-    <t>https://gaubongonline.vn/</t>
-  </si>
-  <si>
-    <t>INPUT_TEXT</t>
-  </si>
-  <si>
-    <t>txtTimKiem</t>
-  </si>
-  <si>
-    <t>gấu bông nhỏ</t>
-  </si>
-  <si>
-    <t>CLICK</t>
-  </si>
-  <si>
-    <t>btnTimKiem</t>
-  </si>
-  <si>
-    <t>WAIT_FOR_ELEMENT_VISIBLE</t>
-  </si>
-  <si>
-    <t>cboTimThay</t>
-  </si>
-  <si>
-    <t>VERIFY_ELEMENT_PRESENT</t>
-  </si>
-  <si>
-    <t>VERIFY_TEXT_CONTAINS</t>
-  </si>
-  <si>
-    <t>CLOSE_BROWSER</t>
-  </si>
-  <si>
-    <t>CLEAR_TEXT</t>
-  </si>
-  <si>
-    <t>txtKoTimThay</t>
-  </si>
-  <si>
-    <t>Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.</t>
-  </si>
-  <si>
-    <t>gấu ông máy bay hạ cánh</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -118,21 +49,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -420,95 +410,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LOCATOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>txtTimKiem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gấu bông dâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLICK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>btnTimKiem</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_VISIBLE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cboTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -516,92 +532,117 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LOCATOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CLEAR_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>txtTimKiem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLICK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>btnTimKiem</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_VISIBLE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cboTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -609,109 +650,125 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="59" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="61" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LOCATOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>txtTimKiem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gấu bông hồng lạ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLICK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>btnTimKiem</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>txtKoTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gấu bông dâu</t>
+          <t>gấu trắng</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLEAR_TEXT</t>
+          <t>INPUT_TEXT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -655,13 +655,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="61" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -718,7 +718,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gấu bông hồng lạ</t>
+          <t>đáy</t>
         </is>
       </c>
     </row>
@@ -752,11 +752,7 @@
           <t>txtKoTimThay</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -764,11 +760,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>txtKoTimThay</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>CLOSE_BROWSER</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ án 4\DoAn4\scripts\DoAn4_Bemori\AI\TestCase\scripts\SCR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7B1448-C963-4506-B1C4-72A697542693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00165F03-9BF8-4A02-B51E-11EF0B330557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_001" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <t>txtTimKiem</t>
   </si>
   <si>
-    <t>gấu tròn</t>
+    <t>gấu trúc</t>
   </si>
   <si>
     <t>CLICK</t>
@@ -60,13 +60,13 @@
     <t>VERIFY_ELEMENT_VISIBLE</t>
   </si>
   <si>
+    <t>cboTimThay</t>
+  </si>
+  <si>
     <t>CLOSE_BROWSER</t>
   </si>
   <si>
-    <t>cboTimThay</t>
-  </si>
-  <si>
-    <t>đáy</t>
+    <t>dragonfruit</t>
   </si>
   <si>
     <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
@@ -482,7 +482,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -490,7 +490,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -564,7 +564,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -572,7 +572,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +660,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/scripts/SCR/SCR_TimKiem.xlsx
@@ -1,99 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ án 4\DoAn4\scripts\DoAn4_Bemori\AI\TestCase\scripts\SCR\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00165F03-9BF8-4A02-B51E-11EF0B330557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TC_001" sheetId="1" r:id="rId1"/>
-    <sheet name="TC_002" sheetId="2" r:id="rId2"/>
-    <sheet name="TC_003" sheetId="3" r:id="rId3"/>
+    <sheet name="TC_001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TC_002" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC_003" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
-  <si>
-    <t>STEP</t>
-  </si>
-  <si>
-    <t>KEYWORD</t>
-  </si>
-  <si>
-    <t>LOCATOR</t>
-  </si>
-  <si>
-    <t>VALUE</t>
-  </si>
-  <si>
-    <t>OPEN_URL</t>
-  </si>
-  <si>
-    <t>https://gaubongonline.vn/</t>
-  </si>
-  <si>
-    <t>INPUT_TEXT</t>
-  </si>
-  <si>
-    <t>txtTimKiem</t>
-  </si>
-  <si>
-    <t>gấu trúc</t>
-  </si>
-  <si>
-    <t>CLICK</t>
-  </si>
-  <si>
-    <t>btnTimKiem</t>
-  </si>
-  <si>
-    <t>VERIFY_ELEMENT_VISIBLE</t>
-  </si>
-  <si>
-    <t>cboTimThay</t>
-  </si>
-  <si>
-    <t>CLOSE_BROWSER</t>
-  </si>
-  <si>
-    <t>dragonfruit</t>
-  </si>
-  <si>
-    <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
-  </si>
-  <si>
-    <t>lblKoTimThay</t>
-  </si>
-  <si>
-    <t>Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -112,21 +49,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -414,84 +410,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LOCATOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>txtTimKiem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gấu bông đỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLICK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>btnTimKiem</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_VISIBLE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cboTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -499,81 +532,117 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LOCATOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>txtTimKiem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLICK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>btnTimKiem</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_VISIBLE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cboTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -581,87 +650,125 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="59" customWidth="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="59" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>LOCATOR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN_URL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://gaubongonline.vn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INPUT_TEXT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>txtTimKiem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>xylophone</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLICK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>btnTimKiem</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>lblKoTimThay</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE_BROWSER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
